--- a/ig/main/ValueSet-EyeColorVS.xlsx
+++ b/ig/main/ValueSet-EyeColorVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-18T07:48:41+00:00</t>
+    <t>2023-08-24T08:11:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-EyeColorVS.xlsx
+++ b/ig/main/ValueSet-EyeColorVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-24T08:11:25+00:00</t>
+    <t>2023-09-06T14:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
